--- a/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
+++ b/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
@@ -18,9 +18,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
-  <si>
-    <t>Табель трудовой дисциплины на момент 09.06.2024 23:35:27</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+  <si>
+    <t>Табель трудовой дисциплины на момент 10.06.2024 14:32:03</t>
   </si>
   <si>
     <t>Дата</t>
@@ -56,10 +56,10 @@
     <t>00:10:52</t>
   </si>
   <si>
-    <t>11:45:01</t>
-  </si>
-  <si>
-    <t>11:34:09</t>
+    <t>23:42:44</t>
+  </si>
+  <si>
+    <t>23:31:52</t>
   </si>
   <si>
     <t>Пирогов Артём Эдуардович</t>
@@ -71,10 +71,19 @@
     <t>11:36:27</t>
   </si>
   <si>
-    <t>11:44:52</t>
-  </si>
-  <si>
-    <t>00:08:25</t>
+    <t>23:42:28</t>
+  </si>
+  <si>
+    <t>12:06:01</t>
+  </si>
+  <si>
+    <t>10-06-2024</t>
+  </si>
+  <si>
+    <t>14:04:49</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
   </si>
 </sst>
 </file>
@@ -281,6 +290,46 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF333333"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF333333"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF333333"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF333333"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF333333"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF333333"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF333333"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF333333"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF333333"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF333333"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF333333"/>
+      </bottom>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF333333"/>
       </left>
@@ -289,20 +338,6 @@
         <color rgb="FF333333"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF333333"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF333333"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF333333"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF333333"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF333333"/>
       </bottom>
     </border>
@@ -313,32 +348,6 @@
         <color rgb="FF333333"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF333333"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF333333"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF333333"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF333333"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF333333"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF333333"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF333333"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF333333"/>
       </bottom>
     </border>
@@ -994,26 +1003,45 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1"/>
+    <row r="5" spans="1:6" ht="15" customHeight="1">
+      <c r="A5" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="6" spans="1:6" ht="15" customHeight="1"/>
     <row r="7" spans="1:6" ht="15" customHeight="1"/>
   </sheetData>

--- a/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
+++ b/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
@@ -18,9 +18,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
-  <si>
-    <t>Табель трудовой дисциплины на момент 10.06.2024 14:32:03</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+  <si>
+    <t>Табель трудовой дисциплины на момент 10.06.2024 17:55:02
+С: 06.06.2024 По: 07.06.2024</t>
   </si>
   <si>
     <t>Дата</t>
@@ -32,7 +33,9 @@
     <t>Должность</t>
   </si>
   <si>
-    <t>Начала фактических присутствий</t>
+    <t>Начала
+фактических
+присутствий</t>
   </si>
   <si>
     <t>Окончания
@@ -44,15 +47,63 @@
 наработка</t>
   </si>
   <si>
+    <t>07-06-2024</t>
+  </si>
+  <si>
+    <t>Кокорин Александр Валерьевич</t>
+  </si>
+  <si>
+    <t>Программист</t>
+  </si>
+  <si>
+    <t>10:23:35</t>
+  </si>
+  <si>
+    <t>21:48:47</t>
+  </si>
+  <si>
+    <t>11:25:12</t>
+  </si>
+  <si>
+    <t>Пирогов Артём Эдуардович</t>
+  </si>
+  <si>
+    <t>ТекстоПисец</t>
+  </si>
+  <si>
+    <t>23:32:39</t>
+  </si>
+  <si>
+    <t>23:44:14</t>
+  </si>
+  <si>
+    <t>00:11:35</t>
+  </si>
+  <si>
+    <t>08-06-2024</t>
+  </si>
+  <si>
+    <t>17:59:28</t>
+  </si>
+  <si>
+    <t>21:47:08</t>
+  </si>
+  <si>
+    <t>03:47:40</t>
+  </si>
+  <si>
+    <t>21:47:35</t>
+  </si>
+  <si>
+    <t>21:48:41</t>
+  </si>
+  <si>
+    <t>00:01:06</t>
+  </si>
+  <si>
     <t>09-06-2024</t>
   </si>
   <si>
-    <t>Кокорин Александр Валерьевич</t>
-  </si>
-  <si>
-    <t>Программист</t>
-  </si>
-  <si>
     <t>00:10:52</t>
   </si>
   <si>
@@ -62,12 +113,6 @@
     <t>23:31:52</t>
   </si>
   <si>
-    <t>Пирогов Артём Эдуардович</t>
-  </si>
-  <si>
-    <t>ТекстоПисец</t>
-  </si>
-  <si>
     <t>11:36:27</t>
   </si>
   <si>
@@ -83,14 +128,17 @@
     <t>14:04:49</t>
   </si>
   <si>
-    <t>00:00:00</t>
+    <t>17:52:50</t>
+  </si>
+  <si>
+    <t>03:48:01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -99,6 +147,12 @@
     <font>
       <b/>
       <sz val="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -485,48 +539,73 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -540,13 +619,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
   </cellXfs>
@@ -949,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultColWidthPt="48.75" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="20.7109375" widthPt="108.75" customWidth="1"/>
@@ -958,92 +1043,170 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1">
-      <c r="A2" s="34" t="s">
+    <row r="2" spans="1:6" ht="40" customHeight="1">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="44" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="31" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="33" t="s">
+      <c r="E5" s="29" t="s">
         <v>20</v>
       </c>
+      <c r="F5" s="31" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1"/>
-    <row r="7" spans="1:6" ht="15" customHeight="1"/>
+    <row r="6" spans="1:6" ht="15" customHeight="1">
+      <c r="A6" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1">
+      <c r="A7" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="12.75">
+      <c r="A8" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="12.75">
+      <c r="A9" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
+++ b/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
-    <t>Табель трудовой дисциплины на момент 10.06.2024 17:55:02
+    <t>Табель трудовой дисциплины на момент 10.06.2024 23:39:17
 С: 06.06.2024 По: 07.06.2024</t>
   </si>
   <si>
@@ -128,10 +128,10 @@
     <t>14:04:49</t>
   </si>
   <si>
-    <t>17:52:50</t>
-  </si>
-  <si>
-    <t>03:48:01</t>
+    <t>22:52:43</t>
+  </si>
+  <si>
+    <t>08:47:54</t>
   </si>
 </sst>
 </file>

--- a/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
+++ b/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
@@ -18,10 +18,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
-  <si>
-    <t>Табель трудовой дисциплины на момент 10.06.2024 23:39:17
-С: 06.06.2024 По: 07.06.2024</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
+  <si>
+    <t>Табель трудовой дисциплины на момент 12.06.2024 13:28:47
+С: 01.06.2024 По: 04.06.2024</t>
   </si>
   <si>
     <t>Дата</t>
@@ -47,15 +47,27 @@
 наработка</t>
   </si>
   <si>
+    <t>04-06-2024</t>
+  </si>
+  <si>
+    <t>Кокорин Александр Валерьевич</t>
+  </si>
+  <si>
+    <t>Программист</t>
+  </si>
+  <si>
+    <t>13:46:25</t>
+  </si>
+  <si>
+    <t>13:47:04</t>
+  </si>
+  <si>
+    <t>00:00:39</t>
+  </si>
+  <si>
     <t>07-06-2024</t>
   </si>
   <si>
-    <t>Кокорин Александр Валерьевич</t>
-  </si>
-  <si>
-    <t>Программист</t>
-  </si>
-  <si>
     <t>10:23:35</t>
   </si>
   <si>
@@ -68,7 +80,7 @@
     <t>Пирогов Артём Эдуардович</t>
   </si>
   <si>
-    <t>ТекстоПисец</t>
+    <t>Бизнес-аналитик</t>
   </si>
   <si>
     <t>23:32:39</t>
@@ -132,6 +144,24 @@
   </si>
   <si>
     <t>08:47:54</t>
+  </si>
+  <si>
+    <t>12-06-2024</t>
+  </si>
+  <si>
+    <t>13:27:00</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>13:13:12</t>
+  </si>
+  <si>
+    <t>13:26:43</t>
+  </si>
+  <si>
+    <t>00:13:31</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultColWidthPt="48.75" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="20.7109375" widthPt="108.75" customWidth="1"/>
@@ -1089,33 +1119,33 @@
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="28" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="E4" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="F4" s="31" t="s">
         <v>16</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="29" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>9</v>
       </c>
       <c r="D5" s="29" t="s">
         <v>19</v>
@@ -1129,33 +1159,33 @@
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="28" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="28" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D7" s="29" t="s">
         <v>26</v>
@@ -1169,42 +1199,102 @@
     </row>
     <row r="8" spans="1:6" ht="12.75">
       <c r="A8" s="28" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="12.75">
-      <c r="A9" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="37" t="s">
+      <c r="A9" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="12.75">
+      <c r="A10" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C10" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>35</v>
+      <c r="D10" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="12.75">
+      <c r="A11" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="12.75">
+      <c r="A12" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
+++ b/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
@@ -18,10 +18,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
-  <si>
-    <t>Табель трудовой дисциплины на момент 12.06.2024 13:28:47
-С: 01.06.2024 По: 04.06.2024</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
+  <si>
+    <t>Табель трудовой дисциплины на момент 20.06.2024 0:02:36
+С: 01.06.2024 По: 19.06.2024</t>
   </si>
   <si>
     <t>Дата</t>
@@ -47,121 +47,97 @@
 наработка</t>
   </si>
   <si>
-    <t>04-06-2024</t>
-  </si>
-  <si>
-    <t>Кокорин Александр Валерьевич</t>
+    <t>14-06-2024</t>
+  </si>
+  <si>
+    <t>Сыроежкин Павел Андреевич</t>
   </si>
   <si>
     <t>Программист</t>
   </si>
   <si>
-    <t>13:46:25</t>
-  </si>
-  <si>
-    <t>13:47:04</t>
-  </si>
-  <si>
-    <t>00:00:39</t>
-  </si>
-  <si>
-    <t>07-06-2024</t>
-  </si>
-  <si>
-    <t>10:23:35</t>
-  </si>
-  <si>
-    <t>21:48:47</t>
-  </si>
-  <si>
-    <t>11:25:12</t>
-  </si>
-  <si>
-    <t>Пирогов Артём Эдуардович</t>
+    <t>11:39:26</t>
+  </si>
+  <si>
+    <t>23:30:48</t>
+  </si>
+  <si>
+    <t>11:51:22</t>
+  </si>
+  <si>
+    <t>Орлов Михаил Дмитриевич</t>
   </si>
   <si>
     <t>Бизнес-аналитик</t>
   </si>
   <si>
-    <t>23:32:39</t>
-  </si>
-  <si>
-    <t>23:44:14</t>
-  </si>
-  <si>
-    <t>00:11:35</t>
-  </si>
-  <si>
-    <t>08-06-2024</t>
-  </si>
-  <si>
-    <t>17:59:28</t>
-  </si>
-  <si>
-    <t>21:47:08</t>
-  </si>
-  <si>
-    <t>03:47:40</t>
-  </si>
-  <si>
-    <t>21:47:35</t>
-  </si>
-  <si>
-    <t>21:48:41</t>
-  </si>
-  <si>
-    <t>00:01:06</t>
-  </si>
-  <si>
-    <t>09-06-2024</t>
-  </si>
-  <si>
-    <t>00:10:52</t>
-  </si>
-  <si>
-    <t>23:42:44</t>
-  </si>
-  <si>
-    <t>23:31:52</t>
-  </si>
-  <si>
-    <t>11:36:27</t>
-  </si>
-  <si>
-    <t>23:42:28</t>
-  </si>
-  <si>
-    <t>12:06:01</t>
-  </si>
-  <si>
-    <t>10-06-2024</t>
-  </si>
-  <si>
-    <t>14:04:49</t>
-  </si>
-  <si>
-    <t>22:52:43</t>
-  </si>
-  <si>
-    <t>08:47:54</t>
-  </si>
-  <si>
-    <t>12-06-2024</t>
-  </si>
-  <si>
-    <t>13:27:00</t>
-  </si>
-  <si>
-    <t>00:00:00</t>
-  </si>
-  <si>
-    <t>13:13:12</t>
-  </si>
-  <si>
-    <t>13:26:43</t>
-  </si>
-  <si>
-    <t>00:13:31</t>
+    <t>18:32:31</t>
+  </si>
+  <si>
+    <t>23:32:47</t>
+  </si>
+  <si>
+    <t>05:00:16</t>
+  </si>
+  <si>
+    <t>15-06-2024</t>
+  </si>
+  <si>
+    <t>18:56:26</t>
+  </si>
+  <si>
+    <t>04:34:22</t>
+  </si>
+  <si>
+    <t>18:56:46</t>
+  </si>
+  <si>
+    <t>04:36:01</t>
+  </si>
+  <si>
+    <t>16-06-2024</t>
+  </si>
+  <si>
+    <t>11:55:18</t>
+  </si>
+  <si>
+    <t>11:35:30</t>
+  </si>
+  <si>
+    <t>11:55:32</t>
+  </si>
+  <si>
+    <t>11:37:15</t>
+  </si>
+  <si>
+    <t>18-06-2024</t>
+  </si>
+  <si>
+    <t>20:47:19</t>
+  </si>
+  <si>
+    <t>02:43:29</t>
+  </si>
+  <si>
+    <t>20:47:58</t>
+  </si>
+  <si>
+    <t>02:44:49</t>
+  </si>
+  <si>
+    <t>19-06-2024</t>
+  </si>
+  <si>
+    <t>21:21:03</t>
+  </si>
+  <si>
+    <t>02:09:45</t>
+  </si>
+  <si>
+    <t>21:22:07</t>
+  </si>
+  <si>
+    <t>02:10:40</t>
   </si>
 </sst>
 </file>
@@ -1119,147 +1095,147 @@
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="29" t="s">
-        <v>8</v>
-      </c>
       <c r="C4" s="29" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="28" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D5" s="29" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="31" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="12.75">
       <c r="A8" s="28" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="12.75">
       <c r="A9" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>33</v>
-      </c>
       <c r="E9" s="29" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="12.75">
       <c r="A10" s="28" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="12.75">
       <c r="A11" s="28" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B11" s="29" t="s">
         <v>8</v>
@@ -1268,33 +1244,33 @@
         <v>9</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="12.75">
       <c r="A12" s="35" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
+++ b/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
@@ -20,8 +20,8 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
   <si>
-    <t>Табель трудовой дисциплины на момент 20.06.2024 0:02:36
-С: 01.06.2024 По: 19.06.2024</t>
+    <t>Табель трудовой дисциплины на момент 20.06.2024 0:31:22
+С: 01.06.2024 По: 30.06.2024</t>
   </si>
   <si>
     <t>Дата</t>

--- a/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
+++ b/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
@@ -18,10 +18,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
-  <si>
-    <t>Табель трудовой дисциплины на момент 20.06.2024 0:31:22
-С: 01.06.2024 По: 30.06.2024</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="67">
+  <si>
+    <t>Табель трудовой дисциплины на момент 22.06.2024 21:20:54
+С: 01.06.2024 По: 29.06.2024</t>
   </si>
   <si>
     <t>Дата</t>
@@ -59,85 +59,172 @@
     <t>11:39:26</t>
   </si>
   <si>
+    <t>18:37:53</t>
+  </si>
+  <si>
+    <t>06:58:27</t>
+  </si>
+  <si>
+    <t>Орлов Михаил Дмитриевич</t>
+  </si>
+  <si>
+    <t>Бизнес-аналитик</t>
+  </si>
+  <si>
+    <t>18:32:31</t>
+  </si>
+  <si>
+    <t>18:40:18</t>
+  </si>
+  <si>
+    <t>00:07:47</t>
+  </si>
+  <si>
+    <t>15-06-2024</t>
+  </si>
+  <si>
+    <t>18:56:26</t>
+  </si>
+  <si>
+    <t>18:57:49</t>
+  </si>
+  <si>
+    <t>00:01:23</t>
+  </si>
+  <si>
+    <t>18:56:46</t>
+  </si>
+  <si>
+    <t>18:57:36</t>
+  </si>
+  <si>
+    <t>00:00:50</t>
+  </si>
+  <si>
+    <t>16-06-2024</t>
+  </si>
+  <si>
+    <t>11:55:18</t>
+  </si>
+  <si>
+    <t>23:08:48</t>
+  </si>
+  <si>
+    <t>11:13:30</t>
+  </si>
+  <si>
+    <t>11:55:32</t>
+  </si>
+  <si>
+    <t>23:09:06</t>
+  </si>
+  <si>
+    <t>11:13:34</t>
+  </si>
+  <si>
+    <t>18-06-2024</t>
+  </si>
+  <si>
+    <t>20:47:19</t>
+  </si>
+  <si>
+    <t>21:19:17</t>
+  </si>
+  <si>
+    <t>00:31:58</t>
+  </si>
+  <si>
+    <t>20:47:58</t>
+  </si>
+  <si>
+    <t>21:19:28</t>
+  </si>
+  <si>
+    <t>00:31:30</t>
+  </si>
+  <si>
+    <t>19-06-2024</t>
+  </si>
+  <si>
+    <t>21:21:03</t>
+  </si>
+  <si>
     <t>23:30:48</t>
   </si>
   <si>
-    <t>11:51:22</t>
-  </si>
-  <si>
-    <t>Орлов Михаил Дмитриевич</t>
-  </si>
-  <si>
-    <t>Бизнес-аналитик</t>
-  </si>
-  <si>
-    <t>18:32:31</t>
+    <t>02:09:45</t>
+  </si>
+  <si>
+    <t>21:22:07</t>
   </si>
   <si>
     <t>23:32:47</t>
   </si>
   <si>
-    <t>05:00:16</t>
-  </si>
-  <si>
-    <t>15-06-2024</t>
-  </si>
-  <si>
-    <t>18:56:26</t>
-  </si>
-  <si>
-    <t>04:34:22</t>
-  </si>
-  <si>
-    <t>18:56:46</t>
-  </si>
-  <si>
-    <t>04:36:01</t>
-  </si>
-  <si>
-    <t>16-06-2024</t>
-  </si>
-  <si>
-    <t>11:55:18</t>
-  </si>
-  <si>
-    <t>11:35:30</t>
-  </si>
-  <si>
-    <t>11:55:32</t>
-  </si>
-  <si>
-    <t>11:37:15</t>
-  </si>
-  <si>
-    <t>18-06-2024</t>
-  </si>
-  <si>
-    <t>20:47:19</t>
-  </si>
-  <si>
-    <t>02:43:29</t>
-  </si>
-  <si>
-    <t>20:47:58</t>
-  </si>
-  <si>
-    <t>02:44:49</t>
-  </si>
-  <si>
-    <t>19-06-2024</t>
-  </si>
-  <si>
-    <t>21:21:03</t>
-  </si>
-  <si>
-    <t>02:09:45</t>
-  </si>
-  <si>
-    <t>21:22:07</t>
-  </si>
-  <si>
     <t>02:10:40</t>
+  </si>
+  <si>
+    <t>20-06-2024</t>
+  </si>
+  <si>
+    <t>00:35:00</t>
+  </si>
+  <si>
+    <t>20:57:20</t>
+  </si>
+  <si>
+    <t>20:22:20</t>
+  </si>
+  <si>
+    <t>00:35:09</t>
+  </si>
+  <si>
+    <t>20:57:31</t>
+  </si>
+  <si>
+    <t>20:22:22</t>
+  </si>
+  <si>
+    <t>21-06-2024</t>
+  </si>
+  <si>
+    <t>22:10:30</t>
+  </si>
+  <si>
+    <t>23:24:09</t>
+  </si>
+  <si>
+    <t>01:13:39</t>
+  </si>
+  <si>
+    <t>22:10:41</t>
+  </si>
+  <si>
+    <t>23:23:09</t>
+  </si>
+  <si>
+    <t>01:12:28</t>
+  </si>
+  <si>
+    <t>22-06-2024</t>
+  </si>
+  <si>
+    <t>17:32:55</t>
+  </si>
+  <si>
+    <t>21:20:30</t>
+  </si>
+  <si>
+    <t>03:47:35</t>
+  </si>
+  <si>
+    <t>17:33:02</t>
+  </si>
+  <si>
+    <t>20:57:06</t>
+  </si>
+  <si>
+    <t>03:24:04</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultColWidthPt="48.75" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="20.7109375" widthPt="108.75" customWidth="1"/>
@@ -1127,10 +1214,10 @@
         <v>19</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
@@ -1144,18 +1231,18 @@
         <v>14</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" s="29" t="s">
         <v>8</v>
@@ -1164,18 +1251,18 @@
         <v>9</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="12.75">
       <c r="A8" s="28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" s="29" t="s">
         <v>13</v>
@@ -1184,18 +1271,18 @@
         <v>14</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="12.75">
       <c r="A9" s="28" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>8</v>
@@ -1204,18 +1291,18 @@
         <v>9</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="12.75">
       <c r="A10" s="28" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B10" s="29" t="s">
         <v>13</v>
@@ -1224,18 +1311,18 @@
         <v>14</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="12.75">
       <c r="A11" s="28" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B11" s="29" t="s">
         <v>8</v>
@@ -1244,33 +1331,153 @@
         <v>9</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="12.75">
-      <c r="A12" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="37" t="s">
+      <c r="A12" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>37</v>
+      <c r="D12" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="12.75">
+      <c r="A13" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="12.75">
+      <c r="A14" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="12.75">
+      <c r="A15" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="12.75">
+      <c r="A16" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="12.75">
+      <c r="A17" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="12.75">
+      <c r="A18" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
+++ b/ACS_BlazorView/wwwroot/Учёты рабочего времени/Учёт рабочего времени.xlsx
@@ -18,10 +18,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="67">
-  <si>
-    <t>Табель трудовой дисциплины на момент 22.06.2024 21:20:54
-С: 01.06.2024 По: 29.06.2024</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="74">
+  <si>
+    <t>Табель трудовой дисциплины на момент 23.06.2024 20:48:35
+С: 01.06.2024 По: 30.06.2024</t>
   </si>
   <si>
     <t>Дата</t>
@@ -225,6 +225,27 @@
   </si>
   <si>
     <t>03:24:04</t>
+  </si>
+  <si>
+    <t>23-06-2024</t>
+  </si>
+  <si>
+    <t>12:19:17</t>
+  </si>
+  <si>
+    <t>16:57:36</t>
+  </si>
+  <si>
+    <t>04:38:19</t>
+  </si>
+  <si>
+    <t>12:19:25</t>
+  </si>
+  <si>
+    <t>16:57:25</t>
+  </si>
+  <si>
+    <t>04:38:00</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultColWidthPt="48.75" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="20.7109375" widthPt="108.75" customWidth="1"/>
@@ -1461,23 +1482,63 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="12.75">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="31" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="12.75">
+      <c r="A19" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="12.75">
+      <c r="A20" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
